--- a/exports/fila_salus_30_07_2026.xlsx
+++ b/exports/fila_salus_30_07_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Pacientes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pacientes'!$A$1:$D$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pacientes'!$A$1:$D$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,37 +521,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DENIS PEREIRA</t>
+          <t>LEILA SCHEER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DP</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KJJJ9F1</t>
+          <t>KKE5GW4</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MARTIN WERNINGHAUS</t>
+          <t>DENIS PEREIRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>DP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KJKAVW0</t>
+          <t>KJJJ9F1</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -561,17 +561,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MARCIUS VINICIUS DE ASSIS MELHEM</t>
+          <t>MARTIN WERNINGHAUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MVDAM</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KJVMTF3</t>
+          <t>KJKAVW0</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -581,77 +581,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALAN FEIS HADDAD</t>
+          <t>MARCIUS VINICIUS DE ASSIS MELHEM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AFH</t>
+          <t>MVDAM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KJ5F3A0</t>
+          <t>KJVMTF3</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIOMARA ROSA PEREIRA FURTADO</t>
+          <t>ALAN FEIS HADDAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SRPF</t>
+          <t>AFH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KJNL8Z5</t>
+          <t>KJ5F3A0</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIAULAS MORIZE VIEIRA MARCONDES JR</t>
+          <t>SIOMARA ROSA PEREIRA FURTADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DMVMJ</t>
+          <t>SRPF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KJTUP80</t>
+          <t>KJNL8Z5</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JOSE OTAVIO VIMIEIRO</t>
+          <t>DIAULAS MORIZE VIEIRA MARCONDES JR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JOV</t>
+          <t>DMVMJ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KJTUTR8</t>
+          <t>KJTUP80</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -661,17 +661,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FABIO LUIZ BUDIB</t>
+          <t>JOSE OTAVIO VIMIEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FLB</t>
+          <t>JOV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KJUXFM1</t>
+          <t>KJTUTR8</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -681,21 +681,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARTHUR UEDA RIBEIRO</t>
+          <t>FABIO LUIZ BUDIB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AUR</t>
+          <t>FLB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KJ8K2D5</t>
+          <t>KJUXFM1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -781,17 +781,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RAQUEL LOBATO GOES DE ALBUQUERQUE</t>
+          <t>GISELA MARIA DE MORAIS GERAIGIRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RLGDA</t>
+          <t>GMDMG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KKEGWR5</t>
+          <t>KKEGLW3</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -801,17 +801,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANTONIA TAVARES DO AMARAL</t>
+          <t>OLIVIA BANK SAPOZNIK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATDA</t>
+          <t>OBS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KKEG9U1</t>
+          <t>KKEGNK0</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -821,17 +821,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MARLY MENEZES MEGALE</t>
+          <t>GILBERTO DE BARROS RODRIGUES LOPES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>GDBRL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KKEHDN2</t>
+          <t>KKDTEP3</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -841,17 +841,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MARLY MENEZES MEGALE</t>
+          <t>ADAUTO DE CASTRO SOARES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ADCS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KKEHEU3</t>
+          <t>KKDU244</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -861,17 +861,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GISELA MARIA DE MORAIS GERAIGIRE</t>
+          <t>FABIO CUTAIT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GMDMG</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KKEGLW3</t>
+          <t>KKDMDU0</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -881,17 +881,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OLIVIA BANK SAPOZNIK</t>
+          <t>MICHELE MASCARO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KKEGNK0</t>
+          <t>KKEEQY1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -901,17 +901,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ADAUTO DE CASTRO SOARES</t>
+          <t>MARLY MENEZES MEGALE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ADCS</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KKDU244</t>
+          <t>KKEHDN2</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -921,17 +921,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GILBERTO DE BARROS RODRIGUES LOPES</t>
+          <t>ANTONIA TAVARES DO AMARAL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GDBRL</t>
+          <t>ATDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KKDTEP3</t>
+          <t>KKEG9U1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -941,17 +941,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MICHELE MASCARO</t>
+          <t>MARLY MENEZES MEGALE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KKEEQY1</t>
+          <t>KKEHEU3</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -961,17 +961,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FABIO CUTAIT</t>
+          <t>RAQUEL LOBATO GOES DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FC</t>
+          <t>RLGDA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KKDMDU0</t>
+          <t>KKEGWR5</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1081,517 +1081,517 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MARIA EUGENIA CARDAMONE</t>
+          <t>FERNANDO PENTEADO MILLAN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MEC</t>
+          <t>FPM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>K3NSD90</t>
+          <t>KKF2268</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ROBERTO REZENDE PIMENTA</t>
+          <t>NATHALIE DIAZ GODINES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RRP</t>
+          <t>NDG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>K3ZPFP7</t>
+          <t>KK3AU60</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAULO CESAR RIBEIRO</t>
+          <t>HELIO ARAUJO JUNIOR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>HAJ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KGA26Y0</t>
+          <t>KK3CNW7</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAURICIO BUSATO</t>
+          <t>OLIVIA COSTA DE SOUZA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>OCDS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KGKRMR3</t>
+          <t>KK3CEK0</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MARCIA ZANCANER BASTO DE CAMARGO</t>
+          <t>MARIA EUGENIA CARDAMONE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MZBDC</t>
+          <t>MEC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KGV25C4</t>
+          <t>K3NSD90</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JOAO ANTONIO RAMOS TINOCO GANDOLFI</t>
+          <t>ROBERTO REZENDE PIMENTA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JARTG</t>
+          <t>RRP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KHD5ED6</t>
+          <t>K3ZPFP7</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NARCISO ESCALEIRA</t>
+          <t>PAULO CESAR RIBEIRO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KHFJ6H8</t>
+          <t>KGA26Y0</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ANTONIO FRANCISCO GALVANESE GALVAO BUENO</t>
+          <t>MAURICIO BUSATO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AFGGB</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KHLYDF3</t>
+          <t>KGKRMR3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FABIO HASE</t>
+          <t>MARCIA ZANCANER BASTO DE CAMARGO</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>MZBDC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KH6RAP7</t>
+          <t>KGV25C4</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JONAS DIAS DE BRITO</t>
+          <t>JOAO ANTONIO RAMOS TINOCO GANDOLFI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JDDB</t>
+          <t>JARTG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KHP6ZT4</t>
+          <t>KHD5ED6</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HAROLDO GUILHERME VIEIRA FAZANO</t>
+          <t>NARCISO ESCALEIRA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HGVF</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KHYWFD0</t>
+          <t>KHFJ6H8</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LEILA MARIA FORTE COLOMBANI LOUREIRO</t>
+          <t>ANTONIO FRANCISCO GALVANESE GALVAO BUENO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LMFCL</t>
+          <t>AFGGB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>K43S4V6</t>
+          <t>KHLYDF3</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JUNG DON PARK</t>
+          <t>FABIO HASE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JDP</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K4RGUH8</t>
+          <t>KH6RAP7</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMAURI RODRIGUES DE MOURA</t>
+          <t>JONAS DIAS DE BRITO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ARDM</t>
+          <t>JDDB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KJ43ZR8</t>
+          <t>KHP6ZT4</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARISTOTELES DE OLIVEIRA</t>
+          <t>HAROLDO GUILHERME VIEIRA FAZANO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADO</t>
+          <t>HGVF</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>K47X9A6</t>
+          <t>KHYWFD0</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CARLOS HENRIQUE WESTPHAL</t>
+          <t>LEILA MARIA FORTE COLOMBANI LOUREIRO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHW</t>
+          <t>LMFCL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>K4SQBV2</t>
+          <t>K43S4V6</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LIA RENATA ANGELINI GIACAGLIA</t>
+          <t>JUNG DON PARK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LRAG</t>
+          <t>JDP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>K4UJCG1</t>
+          <t>K4RGUH8</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MARIAM JANIKIAN</t>
+          <t>AMAURI RODRIGUES DE MOURA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>ARDM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>K4SQZ55</t>
+          <t>KJ43ZR8</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CARLOS GIOBBI</t>
+          <t>ARISTOTELES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>ADO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KJKDN26</t>
+          <t>K47X9A6</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OSWALDO NAGAO</t>
+          <t>CARLOS HENRIQUE WESTPHAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>CHW</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KJD5ZB8</t>
+          <t>K4SQBV2</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FAUZE HADDAD</t>
+          <t>LIA RENATA ANGELINI GIACAGLIA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>LRAG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KJ4WNE2</t>
+          <t>K4UJCG1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ROBERTO TADEU FARIA DA SILVA</t>
+          <t>MARIAM JANIKIAN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTFDS</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KJJD8X3</t>
+          <t>K4SQZ55</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BOANERGES BATISTA PEREIRA FILHO</t>
+          <t>CARLOS GIOBBI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BBPF</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KJJCVJ9</t>
+          <t>KJKDN26</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VERA CECILIA VASCONCELLOS ARRUDA</t>
+          <t>OSWALDO NAGAO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VCVA</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KJJCZ46</t>
+          <t>KJD5ZB8</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ANA ELIZA ROSSO DELEUSE</t>
+          <t>FAUZE HADDAD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AERD</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KJJ2LK8</t>
+          <t>KJ4WNE2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RUBENS PATRICIO</t>
+          <t>BOANERGES BATISTA PEREIRA FILHO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>BBPF</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KJJ2UE6</t>
+          <t>KJJCVJ9</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1601,137 +1601,137 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MARIA BEATRIZ LIMA FURLAN</t>
+          <t>VERA CECILIA VASCONCELLOS ARRUDA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBLF</t>
+          <t>VCVA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KJKBR62</t>
+          <t>KJJCZ46</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MARIA BEATRIZ LIMA FURLAN</t>
+          <t>ANA ELIZA ROSSO DELEUSE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBLF</t>
+          <t>AERD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KJKQH67</t>
+          <t>KJJ2LK8</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TANIA TADDEI HERNDES</t>
+          <t>RUBENS PATRICIO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>RP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KJLBJM0</t>
+          <t>KJJ2UE6</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDEMA AUN JACOB</t>
+          <t>ROBERTO TADEU FARIA DA SILVA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EAJ</t>
+          <t>RTFDS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KJLUCY0</t>
+          <t>KJJD8X3</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JOSE MARIA PEDROSA GOMES</t>
+          <t>MARIA BEATRIZ LIMA FURLAN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JMPG</t>
+          <t>MBLF</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KJK9RT5</t>
+          <t>KJKBR62</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MINEKO MATSUO</t>
+          <t>MARIA BEATRIZ LIMA FURLAN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MM</t>
+          <t>MBLF</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KJL9AG1</t>
+          <t>KJKQH67</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ISAURA NASCIMENTO ISSA</t>
+          <t>EDEMA AUN JACOB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>INI</t>
+          <t>EAJ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KJ56PU9</t>
+          <t>KJLUCY0</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1741,137 +1741,137 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ISABEL TREVISO LATORRE</t>
+          <t>JOSE MARIA PEDROSA GOMES</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ITL</t>
+          <t>JMPG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KJNJP63</t>
+          <t>KJK9RT5</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MAURICE SAAD</t>
+          <t>MINEKO MATSUO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KJNRBX5</t>
+          <t>KJL9AG1</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VERA JEREISSATI HADDAD</t>
+          <t>TANIA TADDEI HERNDES</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VJH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KJTJUB6</t>
+          <t>KJLBJM0</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GERALDO GAION</t>
+          <t>ISAURA NASCIMENTO ISSA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GG</t>
+          <t>INI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KJTHBG7</t>
+          <t>KJ56PU9</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ROBERTO MAYNARD FRANK</t>
+          <t>ISABEL TREVISO LATORRE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RMF</t>
+          <t>ITL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KJTEMB6</t>
+          <t>KJNJP63</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LAURA MONTEIRO BRANDT MANZONI</t>
+          <t>MAURICE SAAD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LMBM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KJSRU52</t>
+          <t>KJNRBX5</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ADRIANO CARDOSO MATTA</t>
+          <t>JOSE ALVARO BARBOSA DE ALMEIDA PEDROSA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>JABDAP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KJTFQJ0</t>
+          <t>KJTAGJ3</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1881,17 +1881,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JONAS DIAS DE BRITO</t>
+          <t>VERA JEREISSATI HADDAD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JDDB</t>
+          <t>VJH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KJTBLS5</t>
+          <t>KJTJUB6</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -1921,17 +1921,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JOSE ALVARO BARBOSA DE ALMEIDA PEDROSA</t>
+          <t>GERALDO GAION</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JABDAP</t>
+          <t>GG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KJTAGJ3</t>
+          <t>KJTHBG7</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1941,197 +1941,197 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LEONICE ALVARES FERNANDES</t>
+          <t>ROBERTO MAYNARD FRANK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LAF</t>
+          <t>RMF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KJTKUW8</t>
+          <t>KJTEMB6</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JOSE MARTINS PINHEIRO</t>
+          <t>ADRIANO CARDOSO MATTA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JMP</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KJ8CF41</t>
+          <t>KJTFQJ0</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JOSE LUIZ RANIERI</t>
+          <t>LAURA MONTEIRO BRANDT MANZONI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JLR</t>
+          <t>LMBM</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KJUYBK8</t>
+          <t>KJSRU52</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LUCY RITA COSTA ROBERTI</t>
+          <t>JONAS DIAS DE BRITO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LRCR</t>
+          <t>JDDB</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KJ8BVJ0</t>
+          <t>KJTBLS5</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LUCIA MARIA BARBOZA DE ALBUQUERQUE</t>
+          <t>LEONICE ALVARES FERNANDES</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LMBDA</t>
+          <t>LAF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KJ8GWL1</t>
+          <t>KJTKUW8</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MARIA EMILIA DE MELLO MARQUES</t>
+          <t>LUCY RITA COSTA ROBERTI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MEDMM</t>
+          <t>LRCR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KJ8MPN0</t>
+          <t>KJ8BVJ0</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUELY BELINHA ROLNIK</t>
+          <t>LUCIA MARIA BARBOZA DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SBR</t>
+          <t>LMBDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KJ85JF0</t>
+          <t>KJ8GWL1</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ELEN FRANCIS DA SILVA</t>
+          <t>JOSE MARTINS PINHEIRO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EFDS</t>
+          <t>JMP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KJ8MJT5</t>
+          <t>KJ8CF41</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JOSE MANOEL MIRANDA</t>
+          <t>JOSE LUIZ RANIERI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JMM</t>
+          <t>JLR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KJ8MNG9</t>
+          <t>KJUYBK8</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RAFAEL HAIB CRIVELI</t>
+          <t>MARIA EMILIA DE MELLO MARQUES</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RHC</t>
+          <t>MEDMM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KJ8L494</t>
+          <t>KJ8MPN0</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2141,17 +2141,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GIOVANNA DESIDERI DE PAIVA</t>
+          <t>SUELY BELINHA ROLNIK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GDDP</t>
+          <t>SBR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KJ8N638</t>
+          <t>KJ85JF0</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -2161,97 +2161,97 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MANUEL ORTEGA BLANCO</t>
+          <t>ELEN FRANCIS DA SILVA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MOB</t>
+          <t>EFDS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KJX3EB1</t>
+          <t>KJ8MJT5</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NADIA SCHAHIM ACCAOUI</t>
+          <t>GIOVANNA DESIDERI DE PAIVA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>GDDP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KJXKGY9</t>
+          <t>KJ8N638</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MADALENA SALUM ID</t>
+          <t>JOSE MANOEL MIRANDA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>JMM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KJXKG63</t>
+          <t>KJ8MNG9</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VANER VITOR VERSORI</t>
+          <t>RAFAEL HAIB CRIVELI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RHC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KJX4WV2</t>
+          <t>KJ8L494</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HENRIQUE RIFE NOBREGA</t>
+          <t>VANER VITOR VERSORI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HRN</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KJVP6L0</t>
+          <t>KJX4WV2</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2261,17 +2261,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JOSE NICOLAU NETTO SABADO</t>
+          <t>HENRIQUE RIFE NOBREGA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JNNS</t>
+          <t>HRN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KJ8VVC8</t>
+          <t>KJVP6L0</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -2281,97 +2281,97 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ELEN FRANCIS DA SILVA</t>
+          <t>JOSE NICOLAU NETTO SABADO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EFDS</t>
+          <t>JNNS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KJXK8C0</t>
+          <t>KJ8VVC8</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ISABEL PRADO CHAPCHAP</t>
+          <t>MANUEL ORTEGA BLANCO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IPC</t>
+          <t>MOB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KKDLDZ0</t>
+          <t>KJX3EB1</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NELLY REQUEJO HERNANDEZ TOVO</t>
+          <t>NADIA SCHAHIM ACCAOUI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NRHT</t>
+          <t>NSA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KKEA7T2</t>
+          <t>KJXKGY9</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DALTON ASSUMCAO CANELHAS</t>
+          <t>MADALENA SALUM ID</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KKD35L1</t>
+          <t>KJXKG63</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OTILIA SOCORRO MONTENEGRO VIEITAS</t>
+          <t>NELLY REQUEJO HERNANDEZ TOVO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OSMV</t>
+          <t>NRHT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KKD9ZA6</t>
+          <t>KKEA7T2</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2381,17 +2381,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CLAUDIA DE LIMA GUIMARAES</t>
+          <t>ISABEL PRADO CHAPCHAP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CDLG</t>
+          <t>IPC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KKE3UD3</t>
+          <t>KKDLDZ0</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2401,17 +2401,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OSVALDO JULIANO</t>
+          <t>DALTON ASSUMCAO CANELHAS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OJ</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KKEGM93</t>
+          <t>KKD35L1</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2421,17 +2421,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EDUARDO ROBSON RAINERI DE ALMEIDA</t>
+          <t>ELEN FRANCIS DA SILVA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ERRDA</t>
+          <t>EFDS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KKEFJN9</t>
+          <t>KJXK8C0</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2478,8 +2478,88 @@
         <v>2</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>OSVALDO JULIANO</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OJ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>KKEGM93</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EDUARDO ROBSON RAINERI DE ALMEIDA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ERRDA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>KKEFJN9</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OTILIA SOCORRO MONTENEGRO VIEITAS</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OSMV</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>KKD9ZA6</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CLAUDIA DE LIMA GUIMARAES</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CDLG</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>KKE3UD3</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D102"/>
+  <autoFilter ref="A1:D106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>